--- a/vbt_bist/academic/output/Anlamli_Ciftler.xlsx
+++ b/vbt_bist/academic/output/Anlamli_Ciftler.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,97 +417,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Sektor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Strateji</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Strateji Kategorisi</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Train Getiri (%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Test Getiri (%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Train Alfa (%)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Test Alfa (%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Test Sharpe</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Test Sortino</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Test Max DD (%)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Test Profit Factor</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Test Islem</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Test Win Rate (%)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Overfit Skor (%)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Tutarli</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Kalite</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Skor</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Guc</t>
         </is>
@@ -4251,60 +4239,60 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SKBNK</t>
+          <t>IZMDC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Banka</t>
+          <t>Madencilik</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>williams_r_14</t>
+          <t>three_soldiers</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Mum</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>706.01</v>
+        <v>-5.48</v>
       </c>
       <c r="F53" t="n">
-        <v>125.65</v>
+        <v>137.03</v>
       </c>
       <c r="G53" t="n">
-        <v>412.97</v>
+        <v>-82.41</v>
       </c>
       <c r="H53" t="n">
-        <v>84.94</v>
+        <v>97.14</v>
       </c>
       <c r="I53" t="n">
-        <v>2.138</v>
+        <v>2.028</v>
       </c>
       <c r="J53" t="n">
-        <v>3.596</v>
+        <v>3.509</v>
       </c>
       <c r="K53" t="n">
-        <v>23.58</v>
+        <v>30.3</v>
       </c>
       <c r="L53" t="n">
-        <v>9.66</v>
+        <v>2.58</v>
       </c>
       <c r="M53" t="n">
         <v>9</v>
       </c>
       <c r="N53" t="n">
-        <v>75</v>
+        <v>55.6</v>
       </c>
       <c r="O53" t="n">
-        <v>82.2</v>
+        <v>-2599</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Evet</t>
+          <t>Hayir</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -4324,60 +4312,60 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IZMDC</t>
+          <t>SKBNK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Madencilik</t>
+          <t>Banka</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>three_soldiers</t>
+          <t>williams_r_14</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mum</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>-5.48</v>
+        <v>706.01</v>
       </c>
       <c r="F54" t="n">
-        <v>137.03</v>
+        <v>125.65</v>
       </c>
       <c r="G54" t="n">
-        <v>-82.41</v>
+        <v>412.97</v>
       </c>
       <c r="H54" t="n">
-        <v>97.14</v>
+        <v>84.94</v>
       </c>
       <c r="I54" t="n">
-        <v>2.028</v>
+        <v>2.138</v>
       </c>
       <c r="J54" t="n">
-        <v>3.509</v>
+        <v>3.596</v>
       </c>
       <c r="K54" t="n">
-        <v>30.3</v>
+        <v>23.58</v>
       </c>
       <c r="L54" t="n">
-        <v>2.58</v>
+        <v>9.66</v>
       </c>
       <c r="M54" t="n">
         <v>9</v>
       </c>
       <c r="N54" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="O54" t="n">
-        <v>-2599</v>
+        <v>82.2</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hayir</t>
+          <t>Evet</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -10612,22 +10600,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>nvi_255</t>
+          <t>historical_vol_rank_20</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Hacim</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>39.72</v>
+        <v>44.6</v>
       </c>
       <c r="H140" t="n">
         <v>94.20999999999999</v>
@@ -10651,7 +10639,7 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
@@ -10685,12 +10673,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>pvi_255</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Hacim</t>
+          <t>Mum</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -10758,22 +10746,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>two_ma_10_50</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Mum</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>-4.88</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>39.72</v>
+        <v>34.84</v>
       </c>
       <c r="H142" t="n">
         <v>94.20999999999999</v>
@@ -10797,7 +10785,7 @@
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
@@ -10831,22 +10819,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>historical_vol_rank_20</t>
+          <t>golden_cross_50_200</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4.88</v>
+        <v>-20.03</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>44.6</v>
+        <v>19.69</v>
       </c>
       <c r="H143" t="n">
         <v>94.20999999999999</v>
@@ -10870,7 +10858,7 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
@@ -10904,22 +10892,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>golden_cross_50_200</t>
+          <t>pin_bar</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Mum</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>-20.03</v>
+        <v>-2.82</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>19.69</v>
+        <v>36.9</v>
       </c>
       <c r="H144" t="n">
         <v>94.20999999999999</v>
@@ -10977,22 +10965,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>pin_bar</t>
+          <t>pvi_255</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Mum</t>
+          <t>Hacim</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>-2.82</v>
+        <v>0</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>36.9</v>
+        <v>39.72</v>
       </c>
       <c r="H145" t="n">
         <v>94.20999999999999</v>
@@ -11016,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
@@ -11050,22 +11038,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>two_ma_10_50</t>
+          <t>nvi_255</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Hacim</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>-4.88</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>34.84</v>
+        <v>39.72</v>
       </c>
       <c r="H146" t="n">
         <v>94.20999999999999</v>
@@ -11089,7 +11077,7 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
@@ -12510,7 +12498,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>three_ma_5_20_50</t>
+          <t>ichimoku_rsi</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -12519,13 +12507,13 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>588.61</v>
+        <v>924.8</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>3.36</v>
+        <v>339.55</v>
       </c>
       <c r="H166" t="n">
         <v>90.3</v>
@@ -12583,7 +12571,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>two_ma_10_50</t>
+          <t>ichimoku_9_26_52</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -12592,13 +12580,13 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>964.6</v>
+        <v>913.47</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>379.35</v>
+        <v>328.23</v>
       </c>
       <c r="H167" t="n">
         <v>90.3</v>
@@ -12656,7 +12644,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ichimoku_9_26_52</t>
+          <t>two_ma_10_50</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -12665,13 +12653,13 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>913.47</v>
+        <v>964.6</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>328.23</v>
+        <v>379.35</v>
       </c>
       <c r="H168" t="n">
         <v>90.3</v>
@@ -12729,7 +12717,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ichimoku_rsi</t>
+          <t>three_ma_5_20_50</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -12738,13 +12726,13 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>924.8</v>
+        <v>588.61</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>339.55</v>
+        <v>3.36</v>
       </c>
       <c r="H169" t="n">
         <v>90.3</v>
@@ -14627,22 +14615,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>donchian_20</t>
+          <t>supertrend_10_3.0</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>-28.38</v>
+        <v>-22.5</v>
       </c>
       <c r="F195" t="n">
         <v>28.58</v>
       </c>
       <c r="G195" t="n">
-        <v>17.28</v>
+        <v>23.17</v>
       </c>
       <c r="H195" t="n">
         <v>58.35</v>
@@ -14666,7 +14654,7 @@
         <v>100</v>
       </c>
       <c r="O195" t="n">
-        <v>-200.7</v>
+        <v>-227</v>
       </c>
       <c r="P195" t="inlineStr">
         <is>
@@ -14700,22 +14688,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>supertrend_10_3.0</t>
+          <t>donchian_20</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>-22.5</v>
+        <v>-28.38</v>
       </c>
       <c r="F196" t="n">
         <v>28.58</v>
       </c>
       <c r="G196" t="n">
-        <v>23.17</v>
+        <v>17.28</v>
       </c>
       <c r="H196" t="n">
         <v>58.35</v>
@@ -14739,7 +14727,7 @@
         <v>100</v>
       </c>
       <c r="O196" t="n">
-        <v>-227</v>
+        <v>-200.7</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
@@ -16160,22 +16148,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>squeeze_20</t>
+          <t>hp_filter_ma</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>0</v>
+        <v>-16.93</v>
       </c>
       <c r="F216" t="n">
         <v>26.4</v>
       </c>
       <c r="G216" t="n">
-        <v>70.05</v>
+        <v>53.12</v>
       </c>
       <c r="H216" t="n">
         <v>55.75</v>
@@ -16199,7 +16187,7 @@
         <v>100</v>
       </c>
       <c r="O216" t="n">
-        <v>0</v>
+        <v>-255.9</v>
       </c>
       <c r="P216" t="inlineStr">
         <is>
@@ -16233,22 +16221,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>hp_filter_ma</t>
+          <t>squeeze_20</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>-16.93</v>
+        <v>0</v>
       </c>
       <c r="F217" t="n">
         <v>26.4</v>
       </c>
       <c r="G217" t="n">
-        <v>53.12</v>
+        <v>70.05</v>
       </c>
       <c r="H217" t="n">
         <v>55.75</v>
@@ -16272,7 +16260,7 @@
         <v>100</v>
       </c>
       <c r="O217" t="n">
-        <v>-255.9</v>
+        <v>0</v>
       </c>
       <c r="P217" t="inlineStr">
         <is>
@@ -16296,65 +16284,65 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>KCAER</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Savunma</t>
+          <t>Enerji</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>stoch_rsi_14</t>
+          <t>bb_width_20</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>-15.71</v>
+        <v>-23.69</v>
       </c>
       <c r="F218" t="n">
-        <v>42.65</v>
+        <v>105.5</v>
       </c>
       <c r="G218" t="n">
-        <v>16.67</v>
+        <v>-58</v>
       </c>
       <c r="H218" t="n">
-        <v>37.98</v>
+        <v>40.32</v>
       </c>
       <c r="I218" t="n">
-        <v>2.17</v>
+        <v>2.553</v>
       </c>
       <c r="J218" t="n">
-        <v>3.607</v>
+        <v>4.244</v>
       </c>
       <c r="K218" t="n">
-        <v>16.27</v>
+        <v>21.68</v>
       </c>
       <c r="L218" t="n">
-        <v>104.77</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N218" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="O218" t="n">
-        <v>-371.5</v>
+        <v>-545.3</v>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Evet</t>
+          <t>Hayir</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>Basarili</t>
+          <t>Yetersiz Islem</t>
         </is>
       </c>
       <c r="R218" t="n">
@@ -16369,65 +16357,65 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>KCAER</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Enerji</t>
+          <t>Savunma</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>bb_width_20</t>
+          <t>stoch_rsi_14</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>-23.69</v>
+        <v>-15.71</v>
       </c>
       <c r="F219" t="n">
-        <v>105.5</v>
+        <v>42.65</v>
       </c>
       <c r="G219" t="n">
-        <v>-58</v>
+        <v>16.67</v>
       </c>
       <c r="H219" t="n">
-        <v>40.32</v>
+        <v>37.98</v>
       </c>
       <c r="I219" t="n">
-        <v>2.553</v>
+        <v>2.17</v>
       </c>
       <c r="J219" t="n">
-        <v>4.244</v>
+        <v>3.607</v>
       </c>
       <c r="K219" t="n">
-        <v>21.68</v>
+        <v>16.27</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>104.77</v>
       </c>
       <c r="M219" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N219" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="O219" t="n">
-        <v>-545.3</v>
+        <v>-371.5</v>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Hayir</t>
+          <t>Evet</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>Yetersiz Islem</t>
+          <t>Basarili</t>
         </is>
       </c>
       <c r="R219" t="n">
@@ -17182,22 +17170,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>morning_star</t>
+          <t>historical_vol_rank_20</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Mum</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>547.1900000000001</v>
+        <v>0</v>
       </c>
       <c r="F230" t="n">
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>-38.06</v>
+        <v>-585.25</v>
       </c>
       <c r="H230" t="n">
         <v>90.3</v>
@@ -17221,7 +17209,7 @@
         <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P230" t="inlineStr">
         <is>
@@ -17255,22 +17243,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>pvi_255</t>
+          <t>trend_intensity_30</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Hacim</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>0</v>
+        <v>396.55</v>
       </c>
       <c r="F231" t="n">
         <v>0</v>
       </c>
       <c r="G231" t="n">
-        <v>-585.25</v>
+        <v>-188.7</v>
       </c>
       <c r="H231" t="n">
         <v>90.3</v>
@@ -17294,7 +17282,7 @@
         <v>0</v>
       </c>
       <c r="O231" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P231" t="inlineStr">
         <is>
@@ -17328,22 +17316,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>nvi_255</t>
+          <t>golden_cross_50_200</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Hacim</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>130.93</v>
+        <v>480</v>
       </c>
       <c r="F232" t="n">
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>-454.32</v>
+        <v>-105.25</v>
       </c>
       <c r="H232" t="n">
         <v>90.3</v>
@@ -17401,22 +17389,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>golden_cross_50_200</t>
+          <t>morning_star</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Mum</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>480</v>
+        <v>547.1900000000001</v>
       </c>
       <c r="F233" t="n">
         <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>-105.25</v>
+        <v>-38.06</v>
       </c>
       <c r="H233" t="n">
         <v>90.3</v>
@@ -17474,22 +17462,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>trend_intensity_30</t>
+          <t>nvi_255</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Hacim</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>396.55</v>
+        <v>130.93</v>
       </c>
       <c r="F234" t="n">
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>-188.7</v>
+        <v>-454.32</v>
       </c>
       <c r="H234" t="n">
         <v>90.3</v>
@@ -17547,7 +17535,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>historical_vol_rank_20</t>
+          <t>bb_width_20</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -17556,13 +17544,13 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>0</v>
+        <v>543.83</v>
       </c>
       <c r="F235" t="n">
         <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>-585.25</v>
+        <v>-41.41</v>
       </c>
       <c r="H235" t="n">
         <v>90.3</v>
@@ -17586,7 +17574,7 @@
         <v>0</v>
       </c>
       <c r="O235" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P235" t="inlineStr">
         <is>
@@ -17620,22 +17608,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>bb_rsi</t>
+          <t>pvi_255</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Hacim</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>16.74</v>
+        <v>0</v>
       </c>
       <c r="F236" t="n">
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>-568.5</v>
+        <v>-585.25</v>
       </c>
       <c r="H236" t="n">
         <v>90.3</v>
@@ -17659,7 +17647,7 @@
         <v>0</v>
       </c>
       <c r="O236" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P236" t="inlineStr">
         <is>
@@ -17693,7 +17681,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>bb_width_20</t>
+          <t>bb_rsi</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -17702,13 +17690,13 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>543.83</v>
+        <v>16.74</v>
       </c>
       <c r="F237" t="n">
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>-41.41</v>
+        <v>-568.5</v>
       </c>
       <c r="H237" t="n">
         <v>90.3</v>
@@ -18131,7 +18119,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>atr_channel_20</t>
+          <t>donchian_20</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -18140,13 +18128,13 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>-2.06</v>
+        <v>-3.67</v>
       </c>
       <c r="F243" t="n">
         <v>104.08</v>
       </c>
       <c r="G243" t="n">
-        <v>-36.37</v>
+        <v>-37.98</v>
       </c>
       <c r="H243" t="n">
         <v>38.9</v>
@@ -18170,7 +18158,7 @@
         <v>100</v>
       </c>
       <c r="O243" t="n">
-        <v>-5146.2</v>
+        <v>-2932.2</v>
       </c>
       <c r="P243" t="inlineStr">
         <is>
@@ -18204,7 +18192,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>donchian_20</t>
+          <t>atr_channel_20</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -18213,13 +18201,13 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>-3.67</v>
+        <v>-2.06</v>
       </c>
       <c r="F244" t="n">
         <v>104.08</v>
       </c>
       <c r="G244" t="n">
-        <v>-37.98</v>
+        <v>-36.37</v>
       </c>
       <c r="H244" t="n">
         <v>38.9</v>
@@ -18243,7 +18231,7 @@
         <v>100</v>
       </c>
       <c r="O244" t="n">
-        <v>-2932.2</v>
+        <v>-5146.2</v>
       </c>
       <c r="P244" t="inlineStr">
         <is>
@@ -18642,22 +18630,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>squeeze_20</t>
+          <t>trend_intensity_30</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>-56.28</v>
+        <v>-14.97</v>
       </c>
       <c r="F250" t="n">
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>25.43</v>
+        <v>66.75</v>
       </c>
       <c r="H250" t="n">
         <v>78</v>
@@ -18715,22 +18703,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>bb_rsi</t>
+          <t>supertrend_rsi</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>-12.16</v>
+        <v>-48.61</v>
       </c>
       <c r="F251" t="n">
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>69.56</v>
+        <v>33.1</v>
       </c>
       <c r="H251" t="n">
         <v>78</v>
@@ -18788,22 +18776,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>hist_vol_20</t>
+          <t>pvi_255</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Hacim</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>-10.77</v>
+        <v>0</v>
       </c>
       <c r="F252" t="n">
         <v>0</v>
       </c>
       <c r="G252" t="n">
-        <v>70.95</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="H252" t="n">
         <v>78</v>
@@ -18827,7 +18815,7 @@
         <v>0</v>
       </c>
       <c r="O252" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P252" t="inlineStr">
         <is>
@@ -18861,7 +18849,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>supertrend_rsi</t>
+          <t>ichimoku_rsi</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -18934,22 +18922,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ichimoku_rsi</t>
+          <t>nvi_255</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Hacim</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>-48.61</v>
+        <v>0</v>
       </c>
       <c r="F254" t="n">
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>33.1</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="H254" t="n">
         <v>78</v>
@@ -18973,7 +18961,7 @@
         <v>0</v>
       </c>
       <c r="O254" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P254" t="inlineStr">
         <is>
@@ -19007,22 +18995,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>trend_intensity_30</t>
+          <t>squeeze_20</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>-14.97</v>
+        <v>-56.28</v>
       </c>
       <c r="F255" t="n">
         <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>66.75</v>
+        <v>25.43</v>
       </c>
       <c r="H255" t="n">
         <v>78</v>
@@ -19080,7 +19068,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>historical_vol_rank_20</t>
+          <t>hist_vol_20</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -19089,13 +19077,13 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>0</v>
+        <v>-10.77</v>
       </c>
       <c r="F256" t="n">
         <v>0</v>
       </c>
       <c r="G256" t="n">
-        <v>81.70999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="H256" t="n">
         <v>78</v>
@@ -19119,7 +19107,7 @@
         <v>0</v>
       </c>
       <c r="O256" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P256" t="inlineStr">
         <is>
@@ -19226,22 +19214,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>pvi_255</t>
+          <t>bb_width_20</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Hacim</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>0</v>
+        <v>-15.19</v>
       </c>
       <c r="F258" t="n">
         <v>0</v>
       </c>
       <c r="G258" t="n">
-        <v>81.70999999999999</v>
+        <v>66.52</v>
       </c>
       <c r="H258" t="n">
         <v>78</v>
@@ -19265,7 +19253,7 @@
         <v>0</v>
       </c>
       <c r="O258" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P258" t="inlineStr">
         <is>
@@ -19299,22 +19287,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>nvi_255</t>
+          <t>bb_rsi</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Hacim</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>0</v>
+        <v>-12.16</v>
       </c>
       <c r="F259" t="n">
         <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>81.70999999999999</v>
+        <v>69.56</v>
       </c>
       <c r="H259" t="n">
         <v>78</v>
@@ -19338,7 +19326,7 @@
         <v>0</v>
       </c>
       <c r="O259" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P259" t="inlineStr">
         <is>
@@ -19372,22 +19360,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ichimoku_9_26_52</t>
+          <t>historical_vol_rank_20</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>-50.56</v>
+        <v>0</v>
       </c>
       <c r="F260" t="n">
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>31.15</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="H260" t="n">
         <v>78</v>
@@ -19411,7 +19399,7 @@
         <v>0</v>
       </c>
       <c r="O260" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P260" t="inlineStr">
         <is>
@@ -19445,22 +19433,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>bb_width_20</t>
+          <t>ichimoku_9_26_52</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>-15.19</v>
+        <v>-50.56</v>
       </c>
       <c r="F261" t="n">
         <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>66.52</v>
+        <v>31.15</v>
       </c>
       <c r="H261" t="n">
         <v>78</v>
@@ -28268,65 +28256,65 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>AEFES</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Tarim</t>
+          <t>Gida</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>trix_15</t>
+          <t>rsi_divergence_14_20</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>170.47</v>
+        <v>45.89</v>
       </c>
       <c r="F382" t="n">
-        <v>28.92</v>
+        <v>51.75</v>
       </c>
       <c r="G382" t="n">
-        <v>182.8</v>
+        <v>-748.86</v>
       </c>
       <c r="H382" t="n">
-        <v>39.57</v>
+        <v>43.71</v>
       </c>
       <c r="I382" t="n">
-        <v>1.165</v>
+        <v>1.458</v>
       </c>
       <c r="J382" t="n">
-        <v>1.846</v>
+        <v>2.555</v>
       </c>
       <c r="K382" t="n">
-        <v>23.56</v>
+        <v>14.22</v>
       </c>
       <c r="L382" t="n">
-        <v>0</v>
+        <v>10.11</v>
       </c>
       <c r="M382" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N382" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="O382" t="n">
-        <v>83</v>
+        <v>-12.8</v>
       </c>
       <c r="P382" t="inlineStr">
         <is>
-          <t>Evet</t>
+          <t>Hayir</t>
         </is>
       </c>
       <c r="Q382" t="inlineStr">
         <is>
-          <t>Yetersiz Islem</t>
+          <t>Basarili</t>
         </is>
       </c>
       <c r="R382" t="n">
@@ -28341,65 +28329,65 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Gida</t>
+          <t>Tarim</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>rsi_divergence_14_20</t>
+          <t>trix_15</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>45.89</v>
+        <v>170.47</v>
       </c>
       <c r="F383" t="n">
-        <v>51.75</v>
+        <v>28.92</v>
       </c>
       <c r="G383" t="n">
-        <v>-748.86</v>
+        <v>182.8</v>
       </c>
       <c r="H383" t="n">
-        <v>43.71</v>
+        <v>39.57</v>
       </c>
       <c r="I383" t="n">
-        <v>1.458</v>
+        <v>1.165</v>
       </c>
       <c r="J383" t="n">
-        <v>2.555</v>
+        <v>1.846</v>
       </c>
       <c r="K383" t="n">
-        <v>14.22</v>
+        <v>23.56</v>
       </c>
       <c r="L383" t="n">
-        <v>10.11</v>
+        <v>0</v>
       </c>
       <c r="M383" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N383" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="O383" t="n">
-        <v>-12.8</v>
+        <v>83</v>
       </c>
       <c r="P383" t="inlineStr">
         <is>
-          <t>Hayir</t>
+          <t>Evet</t>
         </is>
       </c>
       <c r="Q383" t="inlineStr">
         <is>
-          <t>Basarili</t>
+          <t>Yetersiz Islem</t>
         </is>
       </c>
       <c r="R383" t="n">
@@ -30020,60 +30008,60 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>ALBRK</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Banka</t>
+          <t>Tarim</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>rsi_14_30_70</t>
+          <t>inside_bar</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Mum</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>56.83</v>
+        <v>28.47</v>
       </c>
       <c r="F406" t="n">
-        <v>30.52</v>
+        <v>6.76</v>
       </c>
       <c r="G406" t="n">
-        <v>-1.49</v>
+        <v>40.81</v>
       </c>
       <c r="H406" t="n">
-        <v>31.43</v>
+        <v>17.41</v>
       </c>
       <c r="I406" t="n">
-        <v>1.973</v>
+        <v>2.174</v>
       </c>
       <c r="J406" t="n">
-        <v>3.786</v>
+        <v>14.221</v>
       </c>
       <c r="K406" t="n">
-        <v>12</v>
+        <v>0.63</v>
       </c>
       <c r="L406" t="n">
         <v>0</v>
       </c>
       <c r="M406" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N406" t="n">
         <v>100</v>
       </c>
       <c r="O406" t="n">
-        <v>46.3</v>
+        <v>76.2</v>
       </c>
       <c r="P406" t="inlineStr">
         <is>
-          <t>Hayir</t>
+          <t>Evet</t>
         </is>
       </c>
       <c r="Q406" t="inlineStr">
@@ -30093,60 +30081,60 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>ALBRK</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Tarim</t>
+          <t>Banka</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>inside_bar</t>
+          <t>rsi_14_30_70</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Mum</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>28.47</v>
+        <v>56.83</v>
       </c>
       <c r="F407" t="n">
-        <v>6.76</v>
+        <v>30.52</v>
       </c>
       <c r="G407" t="n">
-        <v>40.81</v>
+        <v>-1.49</v>
       </c>
       <c r="H407" t="n">
-        <v>17.41</v>
+        <v>31.43</v>
       </c>
       <c r="I407" t="n">
-        <v>2.174</v>
+        <v>1.973</v>
       </c>
       <c r="J407" t="n">
-        <v>14.221</v>
+        <v>3.786</v>
       </c>
       <c r="K407" t="n">
-        <v>0.63</v>
+        <v>12</v>
       </c>
       <c r="L407" t="n">
         <v>0</v>
       </c>
       <c r="M407" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N407" t="n">
         <v>100</v>
       </c>
       <c r="O407" t="n">
-        <v>76.2</v>
+        <v>46.3</v>
       </c>
       <c r="P407" t="inlineStr">
         <is>
-          <t>Evet</t>
+          <t>Hayir</t>
         </is>
       </c>
       <c r="Q407" t="inlineStr">
@@ -30458,60 +30446,60 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>CEMTS</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Sanayi</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>mean_reversion_20_1.5</t>
+          <t>atr_breakout_14</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Ort. Donus</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>8.49</v>
+        <v>220</v>
       </c>
       <c r="F412" t="n">
-        <v>20.81</v>
+        <v>33.41</v>
       </c>
       <c r="G412" t="n">
-        <v>1.62</v>
+        <v>-58.86</v>
       </c>
       <c r="H412" t="n">
-        <v>30.28</v>
+        <v>50.96</v>
       </c>
       <c r="I412" t="n">
-        <v>1.498</v>
+        <v>0.964</v>
       </c>
       <c r="J412" t="n">
-        <v>2.824</v>
+        <v>1.6</v>
       </c>
       <c r="K412" t="n">
-        <v>15.29</v>
+        <v>29.79</v>
       </c>
       <c r="L412" t="n">
-        <v>4.45</v>
+        <v>1525.05</v>
       </c>
       <c r="M412" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N412" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="O412" t="n">
-        <v>-145.1</v>
+        <v>84.8</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
-          <t>Evet</t>
+          <t>Hayir</t>
         </is>
       </c>
       <c r="Q412" t="inlineStr">
@@ -30531,60 +30519,60 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CEMTS</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Sanayi</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>atr_breakout_14</t>
+          <t>mean_reversion_20_1.5</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Ort. Donus</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>220</v>
+        <v>8.49</v>
       </c>
       <c r="F413" t="n">
-        <v>33.41</v>
+        <v>20.81</v>
       </c>
       <c r="G413" t="n">
-        <v>-58.86</v>
+        <v>1.62</v>
       </c>
       <c r="H413" t="n">
-        <v>50.96</v>
+        <v>30.28</v>
       </c>
       <c r="I413" t="n">
-        <v>0.964</v>
+        <v>1.498</v>
       </c>
       <c r="J413" t="n">
-        <v>1.6</v>
+        <v>2.824</v>
       </c>
       <c r="K413" t="n">
-        <v>29.79</v>
+        <v>15.29</v>
       </c>
       <c r="L413" t="n">
-        <v>1525.05</v>
+        <v>4.45</v>
       </c>
       <c r="M413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N413" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="O413" t="n">
-        <v>84.8</v>
+        <v>-145.1</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>Hayir</t>
+          <t>Evet</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -35714,47 +35702,47 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>YKBNK</t>
+          <t>CANTE</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Banka</t>
+          <t>Teknoloji</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>stoch_14_3_20_80</t>
+          <t>roc_12</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Diger</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="E484" t="n">
-        <v>14.76</v>
+        <v>-30.92</v>
       </c>
       <c r="F484" t="n">
-        <v>24.02</v>
+        <v>12.46</v>
       </c>
       <c r="G484" t="n">
-        <v>-24.97</v>
+        <v>-32.99</v>
       </c>
       <c r="H484" t="n">
-        <v>33.1</v>
+        <v>45.46</v>
       </c>
       <c r="I484" t="n">
-        <v>1.607</v>
+        <v>0.989</v>
       </c>
       <c r="J484" t="n">
-        <v>2.941</v>
+        <v>1.479</v>
       </c>
       <c r="K484" t="n">
-        <v>10.97</v>
+        <v>14.33</v>
       </c>
       <c r="L484" t="n">
-        <v>84.45</v>
+        <v>6.85</v>
       </c>
       <c r="M484" t="n">
         <v>4</v>
@@ -35763,7 +35751,7 @@
         <v>75</v>
       </c>
       <c r="O484" t="n">
-        <v>-62.7</v>
+        <v>-140.3</v>
       </c>
       <c r="P484" t="inlineStr">
         <is>
@@ -35787,47 +35775,47 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>CANTE</t>
+          <t>YKBNK</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Teknoloji</t>
+          <t>Banka</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>roc_12</t>
+          <t>stoch_14_3_20_80</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Diger</t>
         </is>
       </c>
       <c r="E485" t="n">
-        <v>-30.92</v>
+        <v>14.76</v>
       </c>
       <c r="F485" t="n">
-        <v>12.46</v>
+        <v>24.02</v>
       </c>
       <c r="G485" t="n">
-        <v>-32.99</v>
+        <v>-24.97</v>
       </c>
       <c r="H485" t="n">
-        <v>45.46</v>
+        <v>33.1</v>
       </c>
       <c r="I485" t="n">
-        <v>0.989</v>
+        <v>1.607</v>
       </c>
       <c r="J485" t="n">
-        <v>1.479</v>
+        <v>2.941</v>
       </c>
       <c r="K485" t="n">
-        <v>14.33</v>
+        <v>10.97</v>
       </c>
       <c r="L485" t="n">
-        <v>6.85</v>
+        <v>84.45</v>
       </c>
       <c r="M485" t="n">
         <v>4</v>
@@ -35836,7 +35824,7 @@
         <v>75</v>
       </c>
       <c r="O485" t="n">
-        <v>-140.3</v>
+        <v>-62.7</v>
       </c>
       <c r="P485" t="inlineStr">
         <is>
@@ -36590,65 +36578,65 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>MIATK</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Otomotiv</t>
+          <t>Teknoloji</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>mean_reversion_20_1.5</t>
+          <t>ad_line_20</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Ort. Donus</t>
+          <t>Hacim</t>
         </is>
       </c>
       <c r="E496" t="n">
-        <v>13.11</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F496" t="n">
-        <v>25.62</v>
+        <v>5.83</v>
       </c>
       <c r="G496" t="n">
-        <v>-32.92</v>
+        <v>40.39</v>
       </c>
       <c r="H496" t="n">
-        <v>31.97</v>
+        <v>43.95</v>
       </c>
       <c r="I496" t="n">
-        <v>1.634</v>
+        <v>0.535</v>
       </c>
       <c r="J496" t="n">
-        <v>3.007</v>
+        <v>0.84</v>
       </c>
       <c r="K496" t="n">
-        <v>14.56</v>
+        <v>15.55</v>
       </c>
       <c r="L496" t="n">
-        <v>10.38</v>
+        <v>1.26</v>
       </c>
       <c r="M496" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N496" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="O496" t="n">
-        <v>-95.5</v>
+        <v>38.4</v>
       </c>
       <c r="P496" t="inlineStr">
         <is>
-          <t>Hayir</t>
+          <t>Evet</t>
         </is>
       </c>
       <c r="Q496" t="inlineStr">
         <is>
-          <t>Yetersiz Islem</t>
+          <t>Basarili</t>
         </is>
       </c>
       <c r="R496" t="n">
@@ -36663,65 +36651,65 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>MIATK</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Teknoloji</t>
+          <t>Otomotiv</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>ad_line_20</t>
+          <t>mean_reversion_20_1.5</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Hacim</t>
+          <t>Ort. Donus</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>9.460000000000001</v>
+        <v>13.11</v>
       </c>
       <c r="F497" t="n">
-        <v>5.83</v>
+        <v>25.62</v>
       </c>
       <c r="G497" t="n">
-        <v>40.39</v>
+        <v>-32.92</v>
       </c>
       <c r="H497" t="n">
-        <v>43.95</v>
+        <v>31.97</v>
       </c>
       <c r="I497" t="n">
-        <v>0.535</v>
+        <v>1.634</v>
       </c>
       <c r="J497" t="n">
-        <v>0.84</v>
+        <v>3.007</v>
       </c>
       <c r="K497" t="n">
-        <v>15.55</v>
+        <v>14.56</v>
       </c>
       <c r="L497" t="n">
-        <v>1.26</v>
+        <v>10.38</v>
       </c>
       <c r="M497" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N497" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="O497" t="n">
-        <v>38.4</v>
+        <v>-95.5</v>
       </c>
       <c r="P497" t="inlineStr">
         <is>
-          <t>Evet</t>
+          <t>Hayir</t>
         </is>
       </c>
       <c r="Q497" t="inlineStr">
         <is>
-          <t>Basarili</t>
+          <t>Yetersiz Islem</t>
         </is>
       </c>
       <c r="R497" t="n">
@@ -38060,22 +38048,22 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>nvi_255</t>
+          <t>bb_rsi</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Hacim</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E516" t="n">
-        <v>0</v>
+        <v>7.35</v>
       </c>
       <c r="F516" t="n">
         <v>0</v>
       </c>
       <c r="G516" t="n">
-        <v>-690.7</v>
+        <v>-683.35</v>
       </c>
       <c r="H516" t="n">
         <v>63.35</v>
@@ -38099,7 +38087,7 @@
         <v>0</v>
       </c>
       <c r="O516" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P516" t="inlineStr">
         <is>
@@ -38133,22 +38121,22 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>bb_rsi</t>
+          <t>trend_intensity_30</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E517" t="n">
-        <v>7.35</v>
+        <v>146.9</v>
       </c>
       <c r="F517" t="n">
         <v>0</v>
       </c>
       <c r="G517" t="n">
-        <v>-683.35</v>
+        <v>-543.8</v>
       </c>
       <c r="H517" t="n">
         <v>63.35</v>
@@ -38206,7 +38194,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>golden_cross_50_200</t>
+          <t>ichimoku_rsi</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -38215,13 +38203,13 @@
         </is>
       </c>
       <c r="E518" t="n">
-        <v>-10.33</v>
+        <v>183.82</v>
       </c>
       <c r="F518" t="n">
         <v>0</v>
       </c>
       <c r="G518" t="n">
-        <v>-701.04</v>
+        <v>-506.88</v>
       </c>
       <c r="H518" t="n">
         <v>63.35</v>
@@ -38245,7 +38233,7 @@
         <v>0</v>
       </c>
       <c r="O518" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="P518" t="inlineStr">
         <is>
@@ -38279,7 +38267,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>trend_intensity_30</t>
+          <t>golden_cross_50_200</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -38288,13 +38276,13 @@
         </is>
       </c>
       <c r="E519" t="n">
-        <v>146.9</v>
+        <v>-10.33</v>
       </c>
       <c r="F519" t="n">
         <v>0</v>
       </c>
       <c r="G519" t="n">
-        <v>-543.8</v>
+        <v>-701.04</v>
       </c>
       <c r="H519" t="n">
         <v>63.35</v>
@@ -38318,7 +38306,7 @@
         <v>0</v>
       </c>
       <c r="O519" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P519" t="inlineStr">
         <is>
@@ -38352,22 +38340,22 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>ichimoku_rsi</t>
+          <t>nvi_255</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Hacim</t>
         </is>
       </c>
       <c r="E520" t="n">
-        <v>183.82</v>
+        <v>0</v>
       </c>
       <c r="F520" t="n">
         <v>0</v>
       </c>
       <c r="G520" t="n">
-        <v>-506.88</v>
+        <v>-690.7</v>
       </c>
       <c r="H520" t="n">
         <v>63.35</v>
@@ -38391,7 +38379,7 @@
         <v>0</v>
       </c>
       <c r="O520" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P520" t="inlineStr">
         <is>
@@ -39583,17 +39571,17 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>ALFAS</t>
+          <t>TUPRS</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Savunma</t>
+          <t>Enerji</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>kst</t>
+          <t>dpo_20</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -39602,37 +39590,37 @@
         </is>
       </c>
       <c r="E537" t="n">
-        <v>157.15</v>
+        <v>32.04</v>
       </c>
       <c r="F537" t="n">
-        <v>21.35</v>
+        <v>70.36</v>
       </c>
       <c r="G537" t="n">
-        <v>-340.66</v>
+        <v>-56.42</v>
       </c>
       <c r="H537" t="n">
-        <v>47.16</v>
+        <v>-15.42</v>
       </c>
       <c r="I537" t="n">
-        <v>0.75</v>
+        <v>3.879</v>
       </c>
       <c r="J537" t="n">
-        <v>1.26</v>
+        <v>7.571</v>
       </c>
       <c r="K537" t="n">
-        <v>24.86</v>
+        <v>8.43</v>
       </c>
       <c r="L537" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N537" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="O537" t="n">
-        <v>86.40000000000001</v>
+        <v>-119.6</v>
       </c>
       <c r="P537" t="inlineStr">
         <is>
@@ -39641,7 +39629,7 @@
       </c>
       <c r="Q537" t="inlineStr">
         <is>
-          <t>Basarili</t>
+          <t>Yetersiz Islem</t>
         </is>
       </c>
       <c r="R537" t="n">
@@ -39656,17 +39644,17 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>TUPRS</t>
+          <t>ALFAS</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Enerji</t>
+          <t>Savunma</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>dpo_20</t>
+          <t>kst</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -39675,37 +39663,37 @@
         </is>
       </c>
       <c r="E538" t="n">
-        <v>32.04</v>
+        <v>157.15</v>
       </c>
       <c r="F538" t="n">
-        <v>70.36</v>
+        <v>21.35</v>
       </c>
       <c r="G538" t="n">
-        <v>-56.42</v>
+        <v>-340.66</v>
       </c>
       <c r="H538" t="n">
-        <v>-15.42</v>
+        <v>47.16</v>
       </c>
       <c r="I538" t="n">
-        <v>3.879</v>
+        <v>0.75</v>
       </c>
       <c r="J538" t="n">
-        <v>7.571</v>
+        <v>1.26</v>
       </c>
       <c r="K538" t="n">
-        <v>8.43</v>
+        <v>24.86</v>
       </c>
       <c r="L538" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M538" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N538" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="O538" t="n">
-        <v>-119.6</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P538" t="inlineStr">
         <is>
@@ -39714,7 +39702,7 @@
       </c>
       <c r="Q538" t="inlineStr">
         <is>
-          <t>Yetersiz Islem</t>
+          <t>Basarili</t>
         </is>
       </c>
       <c r="R538" t="n">
@@ -41408,56 +41396,56 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>KARSN</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Otomotiv</t>
+          <t>Holding</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>bb_rsi</t>
+          <t>pin_bar</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Mum</t>
         </is>
       </c>
       <c r="E562" t="n">
-        <v>70.67</v>
+        <v>30.52</v>
       </c>
       <c r="F562" t="n">
-        <v>17.72</v>
+        <v>17.01</v>
       </c>
       <c r="G562" t="n">
-        <v>-131.61</v>
+        <v>-10.42</v>
       </c>
       <c r="H562" t="n">
-        <v>33.7</v>
+        <v>21.66</v>
       </c>
       <c r="I562" t="n">
-        <v>1.372</v>
+        <v>1.974</v>
       </c>
       <c r="J562" t="n">
-        <v>2.167</v>
+        <v>3.869</v>
       </c>
       <c r="K562" t="n">
-        <v>6.57</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L562" t="n">
         <v>0</v>
       </c>
       <c r="M562" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N562" t="n">
         <v>100</v>
       </c>
       <c r="O562" t="n">
-        <v>74.90000000000001</v>
+        <v>44.3</v>
       </c>
       <c r="P562" t="inlineStr">
         <is>
@@ -41481,56 +41469,56 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>KARSN</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Holding</t>
+          <t>Otomotiv</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>pin_bar</t>
+          <t>bb_rsi</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>Mum</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E563" t="n">
-        <v>30.52</v>
+        <v>70.67</v>
       </c>
       <c r="F563" t="n">
-        <v>17.01</v>
+        <v>17.72</v>
       </c>
       <c r="G563" t="n">
-        <v>-10.42</v>
+        <v>-131.61</v>
       </c>
       <c r="H563" t="n">
-        <v>21.66</v>
+        <v>33.7</v>
       </c>
       <c r="I563" t="n">
-        <v>1.974</v>
+        <v>1.372</v>
       </c>
       <c r="J563" t="n">
-        <v>3.869</v>
+        <v>2.167</v>
       </c>
       <c r="K563" t="n">
-        <v>9.880000000000001</v>
+        <v>6.57</v>
       </c>
       <c r="L563" t="n">
         <v>0</v>
       </c>
       <c r="M563" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N563" t="n">
         <v>100</v>
       </c>
       <c r="O563" t="n">
-        <v>44.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="P563" t="inlineStr">
         <is>
@@ -43170,22 +43158,22 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>rsi_macd_filtre</t>
+          <t>adx_14_25</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E586" t="n">
-        <v>-44.13</v>
+        <v>-0.27</v>
       </c>
       <c r="F586" t="n">
         <v>0</v>
       </c>
       <c r="G586" t="n">
-        <v>6.53</v>
+        <v>50.38</v>
       </c>
       <c r="H586" t="n">
         <v>49.8</v>
@@ -43243,22 +43231,22 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>ichimoku_9_26_52</t>
+          <t>rsi_macd_filtre</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="E587" t="n">
-        <v>-34.81</v>
+        <v>-44.13</v>
       </c>
       <c r="F587" t="n">
         <v>0</v>
       </c>
       <c r="G587" t="n">
-        <v>15.84</v>
+        <v>6.53</v>
       </c>
       <c r="H587" t="n">
         <v>49.8</v>
@@ -43316,7 +43304,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>golden_cross_50_200</t>
+          <t>supertrend_rsi</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -43325,13 +43313,13 @@
         </is>
       </c>
       <c r="E588" t="n">
-        <v>-41.22</v>
+        <v>-34.73</v>
       </c>
       <c r="F588" t="n">
         <v>0</v>
       </c>
       <c r="G588" t="n">
-        <v>9.44</v>
+        <v>15.92</v>
       </c>
       <c r="H588" t="n">
         <v>49.8</v>
@@ -43389,22 +43377,22 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>doji_reversal</t>
+          <t>three_ma_5_20_50</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Mum</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E589" t="n">
-        <v>27.24</v>
+        <v>-48.86</v>
       </c>
       <c r="F589" t="n">
         <v>0</v>
       </c>
       <c r="G589" t="n">
-        <v>77.89</v>
+        <v>1.8</v>
       </c>
       <c r="H589" t="n">
         <v>49.8</v>
@@ -43428,7 +43416,7 @@
         <v>0</v>
       </c>
       <c r="O589" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P589" t="inlineStr">
         <is>
@@ -43462,7 +43450,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>nvi_255</t>
+          <t>pvi_255</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -43471,13 +43459,13 @@
         </is>
       </c>
       <c r="E590" t="n">
-        <v>0</v>
+        <v>-21.11</v>
       </c>
       <c r="F590" t="n">
         <v>0</v>
       </c>
       <c r="G590" t="n">
-        <v>50.65</v>
+        <v>29.54</v>
       </c>
       <c r="H590" t="n">
         <v>49.8</v>
@@ -43501,7 +43489,7 @@
         <v>0</v>
       </c>
       <c r="O590" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P590" t="inlineStr">
         <is>
@@ -43535,22 +43523,22 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>pvi_255</t>
+          <t>trend_intensity_30</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>Hacim</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E591" t="n">
-        <v>-21.11</v>
+        <v>-28.16</v>
       </c>
       <c r="F591" t="n">
         <v>0</v>
       </c>
       <c r="G591" t="n">
-        <v>29.54</v>
+        <v>22.5</v>
       </c>
       <c r="H591" t="n">
         <v>49.8</v>
@@ -43608,22 +43596,22 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>bullish_engulfing</t>
+          <t>golden_cross_50_200</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Diger</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>0.98</v>
+        <v>-41.22</v>
       </c>
       <c r="F592" t="n">
         <v>0</v>
       </c>
       <c r="G592" t="n">
-        <v>51.63</v>
+        <v>9.44</v>
       </c>
       <c r="H592" t="n">
         <v>49.8</v>
@@ -43647,7 +43635,7 @@
         <v>0</v>
       </c>
       <c r="O592" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P592" t="inlineStr">
         <is>
@@ -43681,22 +43669,22 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>ichimoku_rsi</t>
+          <t>hist_vol_20</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>-31.93</v>
+        <v>18.49</v>
       </c>
       <c r="F593" t="n">
         <v>0</v>
       </c>
       <c r="G593" t="n">
-        <v>18.72</v>
+        <v>69.14</v>
       </c>
       <c r="H593" t="n">
         <v>49.8</v>
@@ -43720,7 +43708,7 @@
         <v>0</v>
       </c>
       <c r="O593" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="P593" t="inlineStr">
         <is>
@@ -43754,22 +43742,22 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>adx_14_25</t>
+          <t>historical_vol_rank_20</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>-0.27</v>
+        <v>7.76</v>
       </c>
       <c r="F594" t="n">
         <v>0</v>
       </c>
       <c r="G594" t="n">
-        <v>50.38</v>
+        <v>58.41</v>
       </c>
       <c r="H594" t="n">
         <v>49.8</v>
@@ -43793,7 +43781,7 @@
         <v>0</v>
       </c>
       <c r="O594" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="P594" t="inlineStr">
         <is>
@@ -43827,7 +43815,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>adx_macd</t>
+          <t>ichimoku_9_26_52</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -43836,13 +43824,13 @@
         </is>
       </c>
       <c r="E595" t="n">
-        <v>7</v>
+        <v>-34.81</v>
       </c>
       <c r="F595" t="n">
         <v>0</v>
       </c>
       <c r="G595" t="n">
-        <v>57.65</v>
+        <v>15.84</v>
       </c>
       <c r="H595" t="n">
         <v>49.8</v>
@@ -43866,7 +43854,7 @@
         <v>0</v>
       </c>
       <c r="O595" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P595" t="inlineStr">
         <is>
@@ -43973,7 +43961,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>supertrend_rsi</t>
+          <t>ichimoku_rsi</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -43982,13 +43970,13 @@
         </is>
       </c>
       <c r="E597" t="n">
-        <v>-34.73</v>
+        <v>-31.93</v>
       </c>
       <c r="F597" t="n">
         <v>0</v>
       </c>
       <c r="G597" t="n">
-        <v>15.92</v>
+        <v>18.72</v>
       </c>
       <c r="H597" t="n">
         <v>49.8</v>
@@ -44046,22 +44034,22 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>hist_vol_20</t>
+          <t>doji_reversal</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Mum</t>
         </is>
       </c>
       <c r="E598" t="n">
-        <v>18.49</v>
+        <v>27.24</v>
       </c>
       <c r="F598" t="n">
         <v>0</v>
       </c>
       <c r="G598" t="n">
-        <v>69.14</v>
+        <v>77.89</v>
       </c>
       <c r="H598" t="n">
         <v>49.8</v>
@@ -44119,22 +44107,22 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>historical_vol_rank_20</t>
+          <t>bullish_engulfing</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Diger</t>
         </is>
       </c>
       <c r="E599" t="n">
-        <v>7.76</v>
+        <v>0.98</v>
       </c>
       <c r="F599" t="n">
         <v>0</v>
       </c>
       <c r="G599" t="n">
-        <v>58.41</v>
+        <v>51.63</v>
       </c>
       <c r="H599" t="n">
         <v>49.8</v>
@@ -44192,7 +44180,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>trend_intensity_30</t>
+          <t>adx_macd</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -44201,13 +44189,13 @@
         </is>
       </c>
       <c r="E600" t="n">
-        <v>-28.16</v>
+        <v>7</v>
       </c>
       <c r="F600" t="n">
         <v>0</v>
       </c>
       <c r="G600" t="n">
-        <v>22.5</v>
+        <v>57.65</v>
       </c>
       <c r="H600" t="n">
         <v>49.8</v>
@@ -44231,7 +44219,7 @@
         <v>0</v>
       </c>
       <c r="O600" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="P600" t="inlineStr">
         <is>
@@ -44265,22 +44253,22 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>three_ma_5_20_50</t>
+          <t>nvi_255</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Hacim</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>-48.86</v>
+        <v>0</v>
       </c>
       <c r="F601" t="n">
         <v>0</v>
       </c>
       <c r="G601" t="n">
-        <v>1.8</v>
+        <v>50.65</v>
       </c>
       <c r="H601" t="n">
         <v>49.8</v>
@@ -44304,7 +44292,7 @@
         <v>0</v>
       </c>
       <c r="O601" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P601" t="inlineStr">
         <is>
@@ -45496,60 +45484,60 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>CIMSA</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Cimento</t>
+          <t>Ulasim</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>rsi_14_30_70</t>
+          <t>bollinger_20_2.0</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E618" t="n">
-        <v>107.67</v>
+        <v>-0.13</v>
       </c>
       <c r="F618" t="n">
-        <v>12.6</v>
+        <v>23.54</v>
       </c>
       <c r="G618" t="n">
-        <v>45.29</v>
+        <v>-12.48</v>
       </c>
       <c r="H618" t="n">
-        <v>28.95</v>
+        <v>25.17</v>
       </c>
       <c r="I618" t="n">
-        <v>1.014</v>
+        <v>1.703</v>
       </c>
       <c r="J618" t="n">
-        <v>1.721</v>
+        <v>3.381</v>
       </c>
       <c r="K618" t="n">
-        <v>17.06</v>
+        <v>15.68</v>
       </c>
       <c r="L618" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M618" t="n">
         <v>3</v>
       </c>
       <c r="N618" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O618" t="n">
-        <v>88.3</v>
+        <v>-17986.5</v>
       </c>
       <c r="P618" t="inlineStr">
         <is>
-          <t>Evet</t>
+          <t>Hayir</t>
         </is>
       </c>
       <c r="Q618" t="inlineStr">
@@ -45569,60 +45557,60 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>CIMSA</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Ulasim</t>
+          <t>Cimento</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>bollinger_20_2.0</t>
+          <t>rsi_14_30_70</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="E619" t="n">
-        <v>-0.13</v>
+        <v>107.67</v>
       </c>
       <c r="F619" t="n">
-        <v>23.54</v>
+        <v>12.6</v>
       </c>
       <c r="G619" t="n">
-        <v>-12.48</v>
+        <v>45.29</v>
       </c>
       <c r="H619" t="n">
-        <v>25.17</v>
+        <v>28.95</v>
       </c>
       <c r="I619" t="n">
-        <v>1.703</v>
+        <v>1.014</v>
       </c>
       <c r="J619" t="n">
-        <v>3.381</v>
+        <v>1.721</v>
       </c>
       <c r="K619" t="n">
-        <v>15.68</v>
+        <v>17.06</v>
       </c>
       <c r="L619" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M619" t="n">
         <v>3</v>
       </c>
       <c r="N619" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O619" t="n">
-        <v>-17986.5</v>
+        <v>88.3</v>
       </c>
       <c r="P619" t="inlineStr">
         <is>
-          <t>Hayir</t>
+          <t>Evet</t>
         </is>
       </c>
       <c r="Q619" t="inlineStr">
@@ -45934,56 +45922,56 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>CANTE</t>
+          <t>YYLGD</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Teknoloji</t>
+          <t>Gida</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>obv_ma_20</t>
+          <t>natr_14</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>Hacim</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E624" t="n">
-        <v>-13.28</v>
+        <v>-17.3</v>
       </c>
       <c r="F624" t="n">
-        <v>10.01</v>
+        <v>23.38</v>
       </c>
       <c r="G624" t="n">
-        <v>-15.35</v>
+        <v>-94.54000000000001</v>
       </c>
       <c r="H624" t="n">
-        <v>43.01</v>
+        <v>35.05</v>
       </c>
       <c r="I624" t="n">
-        <v>0.792</v>
+        <v>0.89</v>
       </c>
       <c r="J624" t="n">
-        <v>1.149</v>
+        <v>1.46</v>
       </c>
       <c r="K624" t="n">
-        <v>11.94</v>
+        <v>19.52</v>
       </c>
       <c r="L624" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M624" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="N624" t="n">
-        <v>100</v>
+        <v>47.4</v>
       </c>
       <c r="O624" t="n">
-        <v>-175.3</v>
+        <v>-235.1</v>
       </c>
       <c r="P624" t="inlineStr">
         <is>
@@ -45992,7 +45980,7 @@
       </c>
       <c r="Q624" t="inlineStr">
         <is>
-          <t>Yetersiz Islem</t>
+          <t>Basarili</t>
         </is>
       </c>
       <c r="R624" t="n">
@@ -46007,56 +45995,56 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>YYLGD</t>
+          <t>CANTE</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Gida</t>
+          <t>Teknoloji</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>natr_14</t>
+          <t>obv_ma_20</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Hacim</t>
         </is>
       </c>
       <c r="E625" t="n">
-        <v>-17.3</v>
+        <v>-13.28</v>
       </c>
       <c r="F625" t="n">
-        <v>23.38</v>
+        <v>10.01</v>
       </c>
       <c r="G625" t="n">
-        <v>-94.54000000000001</v>
+        <v>-15.35</v>
       </c>
       <c r="H625" t="n">
-        <v>35.05</v>
+        <v>43.01</v>
       </c>
       <c r="I625" t="n">
-        <v>0.89</v>
+        <v>0.792</v>
       </c>
       <c r="J625" t="n">
-        <v>1.46</v>
+        <v>1.149</v>
       </c>
       <c r="K625" t="n">
-        <v>19.52</v>
+        <v>11.94</v>
       </c>
       <c r="L625" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M625" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="N625" t="n">
-        <v>47.4</v>
+        <v>100</v>
       </c>
       <c r="O625" t="n">
-        <v>-235.1</v>
+        <v>-175.3</v>
       </c>
       <c r="P625" t="inlineStr">
         <is>
@@ -46065,7 +46053,7 @@
       </c>
       <c r="Q625" t="inlineStr">
         <is>
-          <t>Basarili</t>
+          <t>Yetersiz Islem</t>
         </is>
       </c>
       <c r="R625" t="n">
@@ -46153,56 +46141,56 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>YKBNK</t>
+          <t>GESAN</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Banka</t>
+          <t>Enerji</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>hma_20_50</t>
+          <t>trix_15</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Har. Ort.</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E627" t="n">
-        <v>-14.27</v>
+        <v>-22.96</v>
       </c>
       <c r="F627" t="n">
-        <v>18.2</v>
+        <v>28.43</v>
       </c>
       <c r="G627" t="n">
-        <v>-54</v>
+        <v>-45.09</v>
       </c>
       <c r="H627" t="n">
-        <v>27.28</v>
+        <v>35.8</v>
       </c>
       <c r="I627" t="n">
-        <v>1.575</v>
+        <v>1.149</v>
       </c>
       <c r="J627" t="n">
-        <v>2.793</v>
+        <v>1.712</v>
       </c>
       <c r="K627" t="n">
-        <v>14.35</v>
+        <v>35.36</v>
       </c>
       <c r="L627" t="n">
         <v>0</v>
       </c>
       <c r="M627" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N627" t="n">
         <v>100</v>
       </c>
       <c r="O627" t="n">
-        <v>-227.5</v>
+        <v>-223.8</v>
       </c>
       <c r="P627" t="inlineStr">
         <is>
@@ -46226,56 +46214,56 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>GESAN</t>
+          <t>YKBNK</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Enerji</t>
+          <t>Banka</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>trix_15</t>
+          <t>hma_20_50</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Har. Ort.</t>
         </is>
       </c>
       <c r="E628" t="n">
-        <v>-22.96</v>
+        <v>-14.27</v>
       </c>
       <c r="F628" t="n">
-        <v>28.43</v>
+        <v>18.2</v>
       </c>
       <c r="G628" t="n">
-        <v>-45.09</v>
+        <v>-54</v>
       </c>
       <c r="H628" t="n">
-        <v>35.8</v>
+        <v>27.28</v>
       </c>
       <c r="I628" t="n">
-        <v>1.149</v>
+        <v>1.575</v>
       </c>
       <c r="J628" t="n">
-        <v>1.712</v>
+        <v>2.793</v>
       </c>
       <c r="K628" t="n">
-        <v>35.36</v>
+        <v>14.35</v>
       </c>
       <c r="L628" t="n">
         <v>0</v>
       </c>
       <c r="M628" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N628" t="n">
         <v>100</v>
       </c>
       <c r="O628" t="n">
-        <v>-223.8</v>
+        <v>-227.5</v>
       </c>
       <c r="P628" t="inlineStr">
         <is>
@@ -46445,65 +46433,65 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>BRSAN</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Telekom</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>zscore_20</t>
+          <t>alma_20</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>Ort. Donus</t>
+          <t>Har. Ort.</t>
         </is>
       </c>
       <c r="E631" t="n">
-        <v>26.29</v>
+        <v>25.61</v>
       </c>
       <c r="F631" t="n">
-        <v>11.61</v>
+        <v>29.56</v>
       </c>
       <c r="G631" t="n">
-        <v>1.15</v>
+        <v>-37.02</v>
       </c>
       <c r="H631" t="n">
-        <v>23.15</v>
+        <v>24.25</v>
       </c>
       <c r="I631" t="n">
-        <v>1.261</v>
+        <v>1.406</v>
       </c>
       <c r="J631" t="n">
-        <v>2.106</v>
+        <v>2.424</v>
       </c>
       <c r="K631" t="n">
-        <v>8.44</v>
+        <v>16.36</v>
       </c>
       <c r="L631" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M631" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N631" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="O631" t="n">
-        <v>55.8</v>
+        <v>-15.4</v>
       </c>
       <c r="P631" t="inlineStr">
         <is>
-          <t>Evet</t>
+          <t>Hayir</t>
         </is>
       </c>
       <c r="Q631" t="inlineStr">
         <is>
-          <t>Yetersiz Islem</t>
+          <t>Basarili</t>
         </is>
       </c>
       <c r="R631" t="n">
@@ -46518,65 +46506,65 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Telekom</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>alma_20</t>
+          <t>zscore_20</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Har. Ort.</t>
+          <t>Ort. Donus</t>
         </is>
       </c>
       <c r="E632" t="n">
-        <v>25.61</v>
+        <v>26.29</v>
       </c>
       <c r="F632" t="n">
-        <v>29.56</v>
+        <v>11.61</v>
       </c>
       <c r="G632" t="n">
-        <v>-37.02</v>
+        <v>1.15</v>
       </c>
       <c r="H632" t="n">
-        <v>24.25</v>
+        <v>23.15</v>
       </c>
       <c r="I632" t="n">
-        <v>1.406</v>
+        <v>1.261</v>
       </c>
       <c r="J632" t="n">
-        <v>2.424</v>
+        <v>2.106</v>
       </c>
       <c r="K632" t="n">
-        <v>16.36</v>
+        <v>8.44</v>
       </c>
       <c r="L632" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M632" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N632" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="O632" t="n">
-        <v>-15.4</v>
+        <v>55.8</v>
       </c>
       <c r="P632" t="inlineStr">
         <is>
-          <t>Hayir</t>
+          <t>Evet</t>
         </is>
       </c>
       <c r="Q632" t="inlineStr">
         <is>
-          <t>Basarili</t>
+          <t>Yetersiz Islem</t>
         </is>
       </c>
       <c r="R632" t="n">
@@ -48562,56 +48550,56 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>KCAER</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Savunma</t>
+          <t>Kimya</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>tsi_25_13</t>
+          <t>ao_5_34</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Diger</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>-22.65</v>
+        <v>-19.05</v>
       </c>
       <c r="F660" t="n">
-        <v>19.53</v>
+        <v>6.94</v>
       </c>
       <c r="G660" t="n">
-        <v>9.73</v>
+        <v>51</v>
       </c>
       <c r="H660" t="n">
-        <v>14.86</v>
+        <v>36.3</v>
       </c>
       <c r="I660" t="n">
-        <v>1.621</v>
+        <v>0.549</v>
       </c>
       <c r="J660" t="n">
-        <v>2.961</v>
+        <v>0.798</v>
       </c>
       <c r="K660" t="n">
-        <v>11.06</v>
+        <v>32.27</v>
       </c>
       <c r="L660" t="n">
-        <v>10.49</v>
+        <v>1.35</v>
       </c>
       <c r="M660" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N660" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="O660" t="n">
-        <v>-186.2</v>
+        <v>-136.4</v>
       </c>
       <c r="P660" t="inlineStr">
         <is>
@@ -48635,60 +48623,60 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>KCAER</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Enerji</t>
+          <t>Savunma</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>mean_reversion_20_1.5</t>
+          <t>tsi_25_13</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Ort. Donus</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="E661" t="n">
-        <v>-25.59</v>
+        <v>-22.65</v>
       </c>
       <c r="F661" t="n">
-        <v>16.3</v>
+        <v>19.53</v>
       </c>
       <c r="G661" t="n">
-        <v>-58.59</v>
+        <v>9.73</v>
       </c>
       <c r="H661" t="n">
-        <v>38.82</v>
+        <v>14.86</v>
       </c>
       <c r="I661" t="n">
-        <v>0.923</v>
+        <v>1.621</v>
       </c>
       <c r="J661" t="n">
-        <v>1.705</v>
+        <v>2.961</v>
       </c>
       <c r="K661" t="n">
-        <v>30.15</v>
+        <v>11.06</v>
       </c>
       <c r="L661" t="n">
-        <v>24.09</v>
+        <v>10.49</v>
       </c>
       <c r="M661" t="n">
         <v>4</v>
       </c>
       <c r="N661" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="O661" t="n">
-        <v>-163.7</v>
+        <v>-186.2</v>
       </c>
       <c r="P661" t="inlineStr">
         <is>
-          <t>Hayir</t>
+          <t>Evet</t>
         </is>
       </c>
       <c r="Q661" t="inlineStr">
@@ -48708,60 +48696,60 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>CWENE</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Kimya</t>
+          <t>Enerji</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>ao_5_34</t>
+          <t>mean_reversion_20_1.5</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Diger</t>
+          <t>Ort. Donus</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>-19.05</v>
+        <v>-25.59</v>
       </c>
       <c r="F662" t="n">
-        <v>6.94</v>
+        <v>16.3</v>
       </c>
       <c r="G662" t="n">
-        <v>51</v>
+        <v>-58.59</v>
       </c>
       <c r="H662" t="n">
-        <v>36.3</v>
+        <v>38.82</v>
       </c>
       <c r="I662" t="n">
-        <v>0.549</v>
+        <v>0.923</v>
       </c>
       <c r="J662" t="n">
-        <v>0.798</v>
+        <v>1.705</v>
       </c>
       <c r="K662" t="n">
-        <v>32.27</v>
+        <v>30.15</v>
       </c>
       <c r="L662" t="n">
-        <v>1.35</v>
+        <v>24.09</v>
       </c>
       <c r="M662" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N662" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="O662" t="n">
-        <v>-136.4</v>
+        <v>-163.7</v>
       </c>
       <c r="P662" t="inlineStr">
         <is>
-          <t>Evet</t>
+          <t>Hayir</t>
         </is>
       </c>
       <c r="Q662" t="inlineStr">
@@ -52066,65 +52054,65 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>KZBGY</t>
+          <t>ALFAS</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>GYO</t>
+          <t>Savunma</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>heikin_ashi</t>
+          <t>cmf_20</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Hacim</t>
         </is>
       </c>
       <c r="E708" t="n">
-        <v>117.14</v>
+        <v>136.05</v>
       </c>
       <c r="F708" t="n">
-        <v>22.2</v>
+        <v>12.98</v>
       </c>
       <c r="G708" t="n">
-        <v>57.91</v>
+        <v>-361.77</v>
       </c>
       <c r="H708" t="n">
-        <v>25.88</v>
+        <v>38.8</v>
       </c>
       <c r="I708" t="n">
-        <v>0.64</v>
+        <v>0.794</v>
       </c>
       <c r="J708" t="n">
-        <v>0.945</v>
+        <v>1.556</v>
       </c>
       <c r="K708" t="n">
-        <v>37.27</v>
+        <v>7.61</v>
       </c>
       <c r="L708" t="n">
-        <v>1.19</v>
+        <v>4.22</v>
       </c>
       <c r="M708" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="N708" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="O708" t="n">
-        <v>81</v>
+        <v>90.5</v>
       </c>
       <c r="P708" t="inlineStr">
         <is>
-          <t>Evet</t>
+          <t>Hayir</t>
         </is>
       </c>
       <c r="Q708" t="inlineStr">
         <is>
-          <t>Basarili</t>
+          <t>Yetersiz Islem</t>
         </is>
       </c>
       <c r="R708" t="n">
@@ -52139,65 +52127,65 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>ALFAS</t>
+          <t>KZBGY</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Savunma</t>
+          <t>GYO</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>cmf_20</t>
+          <t>heikin_ashi</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Hacim</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E709" t="n">
-        <v>136.05</v>
+        <v>117.14</v>
       </c>
       <c r="F709" t="n">
-        <v>12.98</v>
+        <v>22.2</v>
       </c>
       <c r="G709" t="n">
-        <v>-361.77</v>
+        <v>57.91</v>
       </c>
       <c r="H709" t="n">
-        <v>38.8</v>
+        <v>25.88</v>
       </c>
       <c r="I709" t="n">
-        <v>0.794</v>
+        <v>0.64</v>
       </c>
       <c r="J709" t="n">
-        <v>1.556</v>
+        <v>0.945</v>
       </c>
       <c r="K709" t="n">
-        <v>7.61</v>
+        <v>37.27</v>
       </c>
       <c r="L709" t="n">
-        <v>4.22</v>
+        <v>1.19</v>
       </c>
       <c r="M709" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="N709" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="O709" t="n">
-        <v>90.5</v>
+        <v>81</v>
       </c>
       <c r="P709" t="inlineStr">
         <is>
-          <t>Hayir</t>
+          <t>Evet</t>
         </is>
       </c>
       <c r="Q709" t="inlineStr">
         <is>
-          <t>Yetersiz Islem</t>
+          <t>Basarili</t>
         </is>
       </c>
       <c r="R709" t="n">
@@ -56300,56 +56288,56 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>CEMTS</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Enerji</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>squeeze_20</t>
+          <t>ppo_12_26_9</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="E766" t="n">
-        <v>-3.53</v>
+        <v>109.1</v>
       </c>
       <c r="F766" t="n">
-        <v>77.39</v>
+        <v>16.03</v>
       </c>
       <c r="G766" t="n">
-        <v>-37.84</v>
+        <v>-169.76</v>
       </c>
       <c r="H766" t="n">
-        <v>12.21</v>
+        <v>33.59</v>
       </c>
       <c r="I766" t="n">
-        <v>1.948</v>
+        <v>0.579</v>
       </c>
       <c r="J766" t="n">
-        <v>3.048</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="K766" t="n">
-        <v>46.31</v>
+        <v>30.9</v>
       </c>
       <c r="L766" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M766" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="N766" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="O766" t="n">
-        <v>-2291.1</v>
+        <v>85.3</v>
       </c>
       <c r="P766" t="inlineStr">
         <is>
@@ -56358,7 +56346,7 @@
       </c>
       <c r="Q766" t="inlineStr">
         <is>
-          <t>Yetersiz Islem</t>
+          <t>Basarili</t>
         </is>
       </c>
       <c r="R766" t="n">
@@ -56373,56 +56361,56 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>CEMTS</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Enerji</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>ppo_12_26_9</t>
+          <t>squeeze_20</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E767" t="n">
-        <v>109.1</v>
+        <v>-3.53</v>
       </c>
       <c r="F767" t="n">
-        <v>16.03</v>
+        <v>77.39</v>
       </c>
       <c r="G767" t="n">
-        <v>-169.76</v>
+        <v>-37.84</v>
       </c>
       <c r="H767" t="n">
-        <v>33.59</v>
+        <v>12.21</v>
       </c>
       <c r="I767" t="n">
-        <v>0.579</v>
+        <v>1.948</v>
       </c>
       <c r="J767" t="n">
-        <v>0.9360000000000001</v>
+        <v>3.048</v>
       </c>
       <c r="K767" t="n">
-        <v>30.9</v>
+        <v>46.31</v>
       </c>
       <c r="L767" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M767" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N767" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="O767" t="n">
-        <v>85.3</v>
+        <v>-2291.1</v>
       </c>
       <c r="P767" t="inlineStr">
         <is>
@@ -56431,7 +56419,7 @@
       </c>
       <c r="Q767" t="inlineStr">
         <is>
-          <t>Basarili</t>
+          <t>Yetersiz Islem</t>
         </is>
       </c>
       <c r="R767" t="n">
@@ -57395,65 +57383,65 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>ISFIN</t>
+          <t>KZBGY</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>GYO</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>ultimate_osc_7_14_28</t>
+          <t>volatility_breakout_0.5</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E781" t="n">
-        <v>264.61</v>
+        <v>195.03</v>
       </c>
       <c r="F781" t="n">
-        <v>54.37</v>
+        <v>18.86</v>
       </c>
       <c r="G781" t="n">
-        <v>-65.33</v>
+        <v>135.81</v>
       </c>
       <c r="H781" t="n">
-        <v>17.99</v>
+        <v>22.53</v>
       </c>
       <c r="I781" t="n">
-        <v>1.627</v>
+        <v>0.6</v>
       </c>
       <c r="J781" t="n">
-        <v>3.001</v>
+        <v>0.91</v>
       </c>
       <c r="K781" t="n">
-        <v>16.6</v>
+        <v>44.9</v>
       </c>
       <c r="L781" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M781" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="N781" t="n">
-        <v>100</v>
+        <v>26.2</v>
       </c>
       <c r="O781" t="n">
-        <v>79.5</v>
+        <v>90.3</v>
       </c>
       <c r="P781" t="inlineStr">
         <is>
-          <t>Hayir</t>
+          <t>Evet</t>
         </is>
       </c>
       <c r="Q781" t="inlineStr">
         <is>
-          <t>Yetersiz Islem</t>
+          <t>Basarili</t>
         </is>
       </c>
       <c r="R781" t="n">
@@ -57468,65 +57456,65 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>KZBGY</t>
+          <t>ISFIN</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>GYO</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>volatility_breakout_0.5</t>
+          <t>ultimate_osc_7_14_28</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="E782" t="n">
-        <v>195.03</v>
+        <v>264.61</v>
       </c>
       <c r="F782" t="n">
-        <v>18.86</v>
+        <v>54.37</v>
       </c>
       <c r="G782" t="n">
-        <v>135.81</v>
+        <v>-65.33</v>
       </c>
       <c r="H782" t="n">
-        <v>22.53</v>
+        <v>17.99</v>
       </c>
       <c r="I782" t="n">
-        <v>0.6</v>
+        <v>1.627</v>
       </c>
       <c r="J782" t="n">
-        <v>0.91</v>
+        <v>3.001</v>
       </c>
       <c r="K782" t="n">
-        <v>44.9</v>
+        <v>16.6</v>
       </c>
       <c r="L782" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="M782" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="N782" t="n">
-        <v>26.2</v>
+        <v>100</v>
       </c>
       <c r="O782" t="n">
-        <v>90.3</v>
+        <v>79.5</v>
       </c>
       <c r="P782" t="inlineStr">
         <is>
-          <t>Evet</t>
+          <t>Hayir</t>
         </is>
       </c>
       <c r="Q782" t="inlineStr">
         <is>
-          <t>Basarili</t>
+          <t>Yetersiz Islem</t>
         </is>
       </c>
       <c r="R782" t="n">
@@ -57541,65 +57529,65 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>CEMTS</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Insaat</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>heikin_ashi</t>
+          <t>volatility_breakout_0.5</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E783" t="n">
-        <v>196.74</v>
+        <v>-31.99</v>
       </c>
       <c r="F783" t="n">
-        <v>15.7</v>
+        <v>-31.5</v>
       </c>
       <c r="G783" t="n">
-        <v>-82.12</v>
+        <v>49.72</v>
       </c>
       <c r="H783" t="n">
-        <v>33.26</v>
+        <v>46.5</v>
       </c>
       <c r="I783" t="n">
-        <v>0.5620000000000001</v>
+        <v>-0.6</v>
       </c>
       <c r="J783" t="n">
-        <v>0.9370000000000001</v>
+        <v>-0.85</v>
       </c>
       <c r="K783" t="n">
-        <v>26.01</v>
+        <v>62.49</v>
       </c>
       <c r="L783" t="n">
-        <v>1.19</v>
+        <v>0.74</v>
       </c>
       <c r="M783" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="N783" t="n">
-        <v>31.2</v>
+        <v>25</v>
       </c>
       <c r="O783" t="n">
-        <v>92</v>
+        <v>-1.5</v>
       </c>
       <c r="P783" t="inlineStr">
         <is>
-          <t>Hayir</t>
+          <t>Evet</t>
         </is>
       </c>
       <c r="Q783" t="inlineStr">
         <is>
-          <t>Basarili</t>
+          <t>Alfa Pozitif</t>
         </is>
       </c>
       <c r="R783" t="n">
@@ -57614,65 +57602,65 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>CEMTS</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Insaat</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>volatility_breakout_0.5</t>
+          <t>heikin_ashi</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E784" t="n">
-        <v>-31.99</v>
+        <v>196.74</v>
       </c>
       <c r="F784" t="n">
-        <v>-31.5</v>
+        <v>15.7</v>
       </c>
       <c r="G784" t="n">
-        <v>49.72</v>
+        <v>-82.12</v>
       </c>
       <c r="H784" t="n">
-        <v>46.5</v>
+        <v>33.26</v>
       </c>
       <c r="I784" t="n">
-        <v>-0.6</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J784" t="n">
-        <v>-0.85</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="K784" t="n">
-        <v>62.49</v>
+        <v>26.01</v>
       </c>
       <c r="L784" t="n">
-        <v>0.74</v>
+        <v>1.19</v>
       </c>
       <c r="M784" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="N784" t="n">
-        <v>25</v>
+        <v>31.2</v>
       </c>
       <c r="O784" t="n">
-        <v>-1.5</v>
+        <v>92</v>
       </c>
       <c r="P784" t="inlineStr">
         <is>
-          <t>Evet</t>
+          <t>Hayir</t>
         </is>
       </c>
       <c r="Q784" t="inlineStr">
         <is>
-          <t>Alfa Pozitif</t>
+          <t>Basarili</t>
         </is>
       </c>
       <c r="R784" t="n">
@@ -59084,7 +59072,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>supertrend_10_3.0</t>
+          <t>two_ma_10_50</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -59093,13 +59081,13 @@
         </is>
       </c>
       <c r="E804" t="n">
-        <v>-62.86</v>
+        <v>-51.79</v>
       </c>
       <c r="F804" t="n">
         <v>0</v>
       </c>
       <c r="G804" t="n">
-        <v>-12.21</v>
+        <v>-1.14</v>
       </c>
       <c r="H804" t="n">
         <v>49.8</v>
@@ -59157,7 +59145,7 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>two_ma_10_50</t>
+          <t>supertrend_10_3.0</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
@@ -59166,13 +59154,13 @@
         </is>
       </c>
       <c r="E805" t="n">
-        <v>-51.79</v>
+        <v>-62.86</v>
       </c>
       <c r="F805" t="n">
         <v>0</v>
       </c>
       <c r="G805" t="n">
-        <v>-1.14</v>
+        <v>-12.21</v>
       </c>
       <c r="H805" t="n">
         <v>49.8</v>
@@ -60023,56 +60011,56 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>GESAN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Enerji</t>
+          <t>Banka</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>stoch_rsi_14</t>
+          <t>tema_20</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Har. Ort.</t>
         </is>
       </c>
       <c r="E817" t="n">
-        <v>10.4</v>
+        <v>30.83</v>
       </c>
       <c r="F817" t="n">
-        <v>18.49</v>
+        <v>10.42</v>
       </c>
       <c r="G817" t="n">
-        <v>-11.73</v>
+        <v>-36.18</v>
       </c>
       <c r="H817" t="n">
-        <v>25.86</v>
+        <v>27.52</v>
       </c>
       <c r="I817" t="n">
-        <v>1.171</v>
+        <v>0.788</v>
       </c>
       <c r="J817" t="n">
-        <v>1.651</v>
+        <v>1.392</v>
       </c>
       <c r="K817" t="n">
-        <v>23.73</v>
+        <v>21</v>
       </c>
       <c r="L817" t="n">
-        <v>4.31</v>
+        <v>1.29</v>
       </c>
       <c r="M817" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N817" t="n">
-        <v>75</v>
+        <v>36.4</v>
       </c>
       <c r="O817" t="n">
-        <v>-77.8</v>
+        <v>66.2</v>
       </c>
       <c r="P817" t="inlineStr">
         <is>
@@ -60096,56 +60084,56 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>AKBNK</t>
+          <t>GESAN</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Banka</t>
+          <t>Enerji</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>tema_20</t>
+          <t>stoch_rsi_14</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>Har. Ort.</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="E818" t="n">
-        <v>30.83</v>
+        <v>10.4</v>
       </c>
       <c r="F818" t="n">
-        <v>10.42</v>
+        <v>18.49</v>
       </c>
       <c r="G818" t="n">
-        <v>-36.18</v>
+        <v>-11.73</v>
       </c>
       <c r="H818" t="n">
-        <v>27.52</v>
+        <v>25.86</v>
       </c>
       <c r="I818" t="n">
-        <v>0.788</v>
+        <v>1.171</v>
       </c>
       <c r="J818" t="n">
-        <v>1.392</v>
+        <v>1.651</v>
       </c>
       <c r="K818" t="n">
-        <v>21</v>
+        <v>23.73</v>
       </c>
       <c r="L818" t="n">
-        <v>1.29</v>
+        <v>4.31</v>
       </c>
       <c r="M818" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="N818" t="n">
-        <v>36.4</v>
+        <v>75</v>
       </c>
       <c r="O818" t="n">
-        <v>66.2</v>
+        <v>-77.8</v>
       </c>
       <c r="P818" t="inlineStr">
         <is>
@@ -60252,22 +60240,22 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>historical_vol_rank_20</t>
+          <t>adx_macd</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E820" t="n">
-        <v>3.21</v>
+        <v>-31.72</v>
       </c>
       <c r="F820" t="n">
         <v>0</v>
       </c>
       <c r="G820" t="n">
-        <v>59.68</v>
+        <v>24.75</v>
       </c>
       <c r="H820" t="n">
         <v>39.22</v>
@@ -60291,7 +60279,7 @@
         <v>0</v>
       </c>
       <c r="O820" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P820" t="inlineStr">
         <is>
@@ -60325,22 +60313,22 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>bullish_engulfing</t>
+          <t>adx_14_25</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>Diger</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E821" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-5.45</v>
       </c>
       <c r="F821" t="n">
         <v>0</v>
       </c>
       <c r="G821" t="n">
-        <v>55.53</v>
+        <v>51.02</v>
       </c>
       <c r="H821" t="n">
         <v>39.22</v>
@@ -60398,7 +60386,7 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>adx_macd</t>
+          <t>trix_15</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -60407,13 +60395,13 @@
         </is>
       </c>
       <c r="E822" t="n">
-        <v>-31.72</v>
+        <v>-11.68</v>
       </c>
       <c r="F822" t="n">
         <v>0</v>
       </c>
       <c r="G822" t="n">
-        <v>24.75</v>
+        <v>44.8</v>
       </c>
       <c r="H822" t="n">
         <v>39.22</v>
@@ -60471,22 +60459,22 @@
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>golden_cross_50_200</t>
+          <t>bullish_engulfing</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Diger</t>
         </is>
       </c>
       <c r="E823" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F823" t="n">
         <v>0</v>
       </c>
       <c r="G823" t="n">
-        <v>56.47</v>
+        <v>55.53</v>
       </c>
       <c r="H823" t="n">
         <v>39.22</v>
@@ -60510,7 +60498,7 @@
         <v>0</v>
       </c>
       <c r="O823" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P823" t="inlineStr">
         <is>
@@ -60544,7 +60532,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>trend_intensity_30</t>
+          <t>ichimoku_rsi</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -60553,13 +60541,13 @@
         </is>
       </c>
       <c r="E824" t="n">
-        <v>-19.49</v>
+        <v>-4.06</v>
       </c>
       <c r="F824" t="n">
         <v>0</v>
       </c>
       <c r="G824" t="n">
-        <v>36.98</v>
+        <v>52.42</v>
       </c>
       <c r="H824" t="n">
         <v>39.22</v>
@@ -60617,22 +60605,22 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>rainbow_ma</t>
+          <t>nvi_255</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Hacim</t>
         </is>
       </c>
       <c r="E825" t="n">
-        <v>-16.29</v>
+        <v>0</v>
       </c>
       <c r="F825" t="n">
         <v>0</v>
       </c>
       <c r="G825" t="n">
-        <v>40.18</v>
+        <v>56.47</v>
       </c>
       <c r="H825" t="n">
         <v>39.22</v>
@@ -60656,7 +60644,7 @@
         <v>0</v>
       </c>
       <c r="O825" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P825" t="inlineStr">
         <is>
@@ -60690,22 +60678,22 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>pvi_255</t>
+          <t>historical_vol_rank_20</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>Hacim</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E826" t="n">
-        <v>-9.359999999999999</v>
+        <v>3.21</v>
       </c>
       <c r="F826" t="n">
         <v>0</v>
       </c>
       <c r="G826" t="n">
-        <v>47.12</v>
+        <v>59.68</v>
       </c>
       <c r="H826" t="n">
         <v>39.22</v>
@@ -60729,7 +60717,7 @@
         <v>0</v>
       </c>
       <c r="O826" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="P826" t="inlineStr">
         <is>
@@ -60763,22 +60751,22 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>trix_15</t>
+          <t>pvi_255</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Hacim</t>
         </is>
       </c>
       <c r="E827" t="n">
-        <v>-11.68</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="F827" t="n">
         <v>0</v>
       </c>
       <c r="G827" t="n">
-        <v>44.8</v>
+        <v>47.12</v>
       </c>
       <c r="H827" t="n">
         <v>39.22</v>
@@ -60826,60 +60814,60 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>YKBNK</t>
+          <t>VESBE</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Banka</t>
+          <t>Elektronik</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>bb_rsi</t>
+          <t>rainbow_ma</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>Volatilite</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="E828" t="n">
-        <v>35.53</v>
+        <v>-16.29</v>
       </c>
       <c r="F828" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="G828" t="n">
-        <v>-4.2</v>
+        <v>40.18</v>
       </c>
       <c r="H828" t="n">
-        <v>12.56</v>
+        <v>39.22</v>
       </c>
       <c r="I828" t="n">
-        <v>1.833</v>
+        <v>0</v>
       </c>
       <c r="J828" t="n">
-        <v>12.855</v>
+        <v>0</v>
       </c>
       <c r="K828" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L828" t="n">
         <v>0</v>
       </c>
       <c r="M828" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N828" t="n">
         <v>0</v>
       </c>
       <c r="O828" t="n">
-        <v>90.2</v>
+        <v>-100</v>
       </c>
       <c r="P828" t="inlineStr">
         <is>
-          <t>Hayir</t>
+          <t>Evet</t>
         </is>
       </c>
       <c r="Q828" t="inlineStr">
@@ -60909,7 +60897,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>ichimoku_rsi</t>
+          <t>golden_cross_50_200</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -60918,13 +60906,13 @@
         </is>
       </c>
       <c r="E829" t="n">
-        <v>-4.06</v>
+        <v>0</v>
       </c>
       <c r="F829" t="n">
         <v>0</v>
       </c>
       <c r="G829" t="n">
-        <v>52.42</v>
+        <v>56.47</v>
       </c>
       <c r="H829" t="n">
         <v>39.22</v>
@@ -60948,7 +60936,7 @@
         <v>0</v>
       </c>
       <c r="O829" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P829" t="inlineStr">
         <is>
@@ -60972,60 +60960,60 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>VESBE</t>
+          <t>YKBNK</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Elektronik</t>
+          <t>Banka</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>nvi_255</t>
+          <t>bb_rsi</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>Hacim</t>
+          <t>Volatilite</t>
         </is>
       </c>
       <c r="E830" t="n">
-        <v>0</v>
+        <v>35.53</v>
       </c>
       <c r="F830" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="G830" t="n">
-        <v>56.47</v>
+        <v>-4.2</v>
       </c>
       <c r="H830" t="n">
-        <v>39.22</v>
+        <v>12.56</v>
       </c>
       <c r="I830" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="J830" t="n">
-        <v>0</v>
+        <v>12.855</v>
       </c>
       <c r="K830" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L830" t="n">
         <v>0</v>
       </c>
       <c r="M830" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N830" t="n">
         <v>0</v>
       </c>
       <c r="O830" t="n">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="P830" t="inlineStr">
         <is>
-          <t>Evet</t>
+          <t>Hayir</t>
         </is>
       </c>
       <c r="Q830" t="inlineStr">
@@ -61055,7 +61043,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>adx_14_25</t>
+          <t>trend_intensity_30</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -61064,13 +61052,13 @@
         </is>
       </c>
       <c r="E831" t="n">
-        <v>-5.45</v>
+        <v>-19.49</v>
       </c>
       <c r="F831" t="n">
         <v>0</v>
       </c>
       <c r="G831" t="n">
-        <v>51.02</v>
+        <v>36.98</v>
       </c>
       <c r="H831" t="n">
         <v>39.22</v>
